--- a/excel_templates/操作日志表.xlsx
+++ b/excel_templates/操作日志表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E551"/>
+  <dimension ref="A1:E610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15371,6 +15371,1604 @@
         </is>
       </c>
     </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>179ed033-abfc-4dd5-99d6-18a387c6dcfb</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>2026-02-24 09:41</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>批量提醒: test</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>LE- 
+XFZN01-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>54a17ab7-6076-444f-8038-b28dd78a33db</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>2026-02-24 09:41</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>批量提醒: lan</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>76ab19c8-cb6d-4a4a-84e8-310b7515ea09</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>2026-02-24 09:41</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>批量提醒: lan</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>仪表-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>444547d0-ef05-4801-921d-74e9ad691746</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>2026-02-24 09:41</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>批量提醒: test</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>手机-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>f7393d2c-8b63-47c8-8f1b-16b991444677</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>2026-02-24 09:41</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>批量提醒: summer</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>手机-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>cc45ea9f-9b8a-43ab-9fba-fbbf48da9ae3</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>2026-02-24 09:41</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>批量提醒: test</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>0b191f2c-35a2-4847-a2de-a77795fb865c</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>2026-02-24 09:41</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>批量提醒: test</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>联想平板-邵阳K12（HA27VAW9）</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>8150a446-7337-4694-8f56-ea1f6c6a849f</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>2026-02-24 09:41</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>批量提醒: lan</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>机械臂（大象机器人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>261da78b-9e1d-4342-bbbd-d23ca9b20dd3</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>2026-02-24 09:41</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>批量提醒: lan</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>iPhone 14 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>9d20ea5b-d794-4506-93d1-34267af80342</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>2026-02-24 09:41</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>批量提醒: test</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>联通测试卡：18696137226</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>63230fa4-2360-41cb-8f00-fbd52d11bfb0</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>2026-02-24 09:41</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>批量提醒: test</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>测试卡17320507707</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>eb15623c-699f-4a90-acde-bfc96fbe4c66</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>发送归还提醒给: test</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>手机-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>0e03fa65-fd1f-434a-806c-f65a8eda05b9</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>批量提醒: test</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>LE- 
+XFZN01-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>0be48ae9-6b1b-4bf7-b1d4-8274f272564a</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>批量提醒: lan</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>064a036d-b77c-406e-be10-3e0512363e47</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>批量提醒: lan</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>仪表-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>bbca0609-a3c5-4d33-9b54-66818ca223b8</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>批量提醒: test</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>手机-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>d72a0f8f-f9d7-459b-9a6a-09343d3a74dd</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>批量提醒: summer</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>手机-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>502c5b9a-5438-4545-a3fa-1638d28a57c0</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>批量提醒: test</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>957681cd-2d6f-4dd1-9e60-d742cce54a85</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>批量提醒: test</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>联想平板-邵阳K12（HA27VAW9）</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>572fe423-c1e6-4de2-834c-31d843c70308</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>批量提醒: lan</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>机械臂（大象机器人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>21aeef8f-1a43-4bb2-bca3-75a7df253733</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>批量提醒: lan</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>iPhone 14 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>e7928c7a-89e5-4ea4-829a-853962b4a159</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>批量提醒: test</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>联通测试卡：18696137226</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>58216836-a5c4-420d-a2a3-389b92a62b56</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>批量提醒: test</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>测试卡17320507707</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>9720dab8-09a6-4e33-a25e-62af744a1f86</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>批量提醒: test</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>LE- 
+XFZN01-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>6743231d-bfdc-4ed8-9b00-871c7ed341e5</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>批量提醒: lan</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>96414200-cd5e-4426-9247-bab0262e4764</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>批量提醒: lan</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>仪表-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>5392277e-7119-4030-9952-f8e3e8a18df8</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>批量提醒: test</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>手机-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>9f2da6c5-532f-409d-8787-d43779156a56</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>批量提醒: summer</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>手机-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>0e839a11-26f3-47d3-96d5-a3f26c21e9f9</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>批量提醒: test</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>95b0d3ed-6023-444e-ba47-5196756808b2</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>批量提醒: test</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>联想平板-邵阳K12（HA27VAW9）</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>ed4b39da-19a8-4b77-ae94-cad877dc4b8a</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>批量提醒: lan</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>机械臂（大象机器人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>e9d39075-094d-4e0d-8152-6b4a5e92d755</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>批量提醒: lan</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>iPhone 14 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>be735b68-6408-44bc-859c-82d299fdf658</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>批量提醒: test</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>联通测试卡：18696137226</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>b7103dc4-96ad-4b6c-9b28-b6e71c43584b</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>批量提醒: test</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>测试卡17320507707</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>cf5b97a5-5236-4afc-82cb-746464d1201d</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:11</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>更新设备信息</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>手机-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>14d0a3ad-0c33-48bd-bec2-1aff39068207</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:12</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>强制归还: test</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>手机-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>4ad2c310-aaaa-40c9-9f6f-eab97af3a707</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:13</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>更新设备信息</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>d5cb53ab-cf4b-4ede-ae49-f78ba55b7757</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:13</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>强制归还: test</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>52494d43-3b1c-4f3c-85d4-a57568f2b819</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:16</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>发送归还提醒给: test</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>联想平板-邵阳K12（HA27VAW9）</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>686d53eb-9f26-4b97-9f37-f3af0675a856</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:17</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>发送归还提醒给: test</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>联想平板-邵阳K12（HA27VAW9）</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>7dce5220-d66b-4684-82fc-3878153316dd</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:18</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>发送归还提醒给: test</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>联想平板-邵阳K12（HA27VAW9）</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>396014df-59ba-460d-b25c-bf71f3b637ab</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:20</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>更新公告: 爱惜设备</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>公告管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>9623ce91-1567-4fec-bc75-7cf0d574a9a4</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:20</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>更新公告: 按时归还</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>公告管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>b7d42138-7fa5-47fc-b0e3-5518706258fb</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:23</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>创建普通公告: 借用设备说明</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>公告管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>ab04aa1c-4d23-4496-af76-bb165f13d47c</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:24</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>创建普通公告: 设备状态</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>公告管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>e45ea87b-fbe8-4003-905c-33768f0feebc</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>2026-02-24 13:46</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>更新设备信息</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>39afb652-954b-4827-9f06-951940e1790b</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>2026-02-24 13:46</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>设备找回自用: lan</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>6526c1d5-1a59-4b66-b8f0-583c4110fb5c</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>2026-02-24 13:48</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>更新设备信息</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>仪表-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>0174f7dd-713a-4488-b3ca-656fc2aa04f8</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>2026-02-24 13:48</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>强制归还: lan</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>仪表-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>fdaf73b7-0c2a-46d2-87de-0bf4ac8097c2</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>2026-02-24 13:52</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>创建普通公告: 温馨提示</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>公告管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>9b197ffe-b2c8-4df7-8bc5-ce342e6925fe</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>2026-02-24 14:42</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>创建普通公告: 查找设备</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>公告管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>5aa49427-6eb0-4916-83a9-e74c03f146c6</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>2026-02-24 14:51</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>上移公告: 温馨提示</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>公告管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>647ccbab-75bb-48f4-8c4e-547da73c6dcf</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>2026-02-24 14:51</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>上移公告: 温馨提示</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>公告管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>24fcf0ea-3c2e-40ff-9a83-552e0f54e4da</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>2026-02-24 14:52</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>上移公告: 温馨提示</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>公告管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>28196aad-7554-4596-93fe-153eed9ede55</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>2026-02-24 14:53</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>下移公告: 查找设备</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>公告管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>61b32bad-4e15-4f7d-9056-4f22b167b944</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>2026-02-24 16:59</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>更新设备信息</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>LE- 
+XFZN01-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>8e764eb9-f5c7-4125-9b42-6d2421e3b7cd</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>2026-02-24 16:59</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>转给自己: test -&gt; lan</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>LE- 
+XFZN01-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>a221e300-d536-4764-98c2-26207bfaea11</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>2026-02-24 17:22</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>更新设备信息</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>b3a60b14-422e-4662-88cd-ae834e45a282</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>2026-02-24 17:22</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>转借设备: lan -&gt; test</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel_templates/操作日志表.xlsx
+++ b/excel_templates/操作日志表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E610"/>
+  <dimension ref="A1:E613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16969,6 +16969,87 @@
         </is>
       </c>
     </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>c76cb0c7-ee89-4cca-b747-a5b137943c9e</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:28</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>更新设备信息</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>71905f2e-9c26-4251-a697-9074d30c0083</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:28</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>转借设备: 保管人 -&gt; test</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>d5fc8383-be8b-492a-b222-412876a652f8</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:34</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>再次公告: 设备使用公告 (版本2)</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>公告管理</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel_templates/操作日志表.xlsx
+++ b/excel_templates/操作日志表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E613"/>
+  <dimension ref="A1:E645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17050,6 +17050,872 @@
         </is>
       </c>
     </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>1f91663e-f41b-48ef-b5b0-7fc7c37acbeb</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:01</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>标记备注为不当内容</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>备注ID: fb7a4cec-ddd6-4c34-99cb-09be849d2bfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>8608b64c-4f64-43aa-9d6c-830065a90089</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:02</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>删除备注</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>备注ID: 52d6f374-87a6-4718-9cfd-c6cf0c508d69</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>a95353d0-d302-4afd-9256-4985afe54853</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:02</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>删除备注</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>备注ID: 52d6f374-87a6-4718-9cfd-c6cf0c508d69</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>fe678c10-4ba5-4b3d-9b1a-faa837aaada5</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:05</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>取消备注不当标记</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>备注ID: fb7a4cec-ddd6-4c34-99cb-09be849d2bfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>e53453f9-7aa4-4b7d-a47e-37f8e8bfcb42</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:14</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>设置管理员</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>07ad0d3d-17ad-44dc-8194-3f48e0f4d29b</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:23</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>更新设备信息</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>LE- 
+XFZN01-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>22d4c4bd-04c7-477b-a01e-a2980b8f6735</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:23</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>强制归还: lan</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>LE- 
+XFZN01-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>d891e752-8028-4f5e-a187-d1fc5b460677</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:24</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>更新设备信息</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>iPhone 14 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>b6f076aa-10de-448a-9469-cdaebe9660d3</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:24</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>转借设备: lan -&gt; test</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>iPhone 14 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>0c6466ae-d180-40dd-af6c-67155b42b92c</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:30</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>更新设备信息</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>ab0d9e56-a354-48f5-9ace-4ee9ae95f2c9</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:30</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>转借设备: test -&gt; lan</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>6b9b4ea7-37ea-4c2a-9d0f-32204993253a</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:33</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>更新设备信息</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>89ee9340-718b-4dbb-8701-9beef63ae10e</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:33</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>转给自己: lan -&gt; test</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>ac755c94-59c1-4b6f-b1f4-ae2941aa6c96</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:06</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>更新设备信息</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>b7b47ca1-85a6-4f7a-abac-d9c27dd57128</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:06</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>转给自己: test -&gt; lan</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>8f412509-9502-423c-b8d3-483979d25f2a</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:15</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>更新设备信息</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>c5a86fef-7dbe-4582-b207-171aaabc9b11</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:16</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>转借设备: lan -&gt; test</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>cb42bf4a-929d-4a55-9acf-da55be5ca067</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:16</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>更新设备信息</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>1b3ba2d1-d1d9-4de7-a1e4-da4140d1c729</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:16</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>归还设备: test</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>b4a454f4-ba9d-42fa-a852-685479ec3257</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:16</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>归还设备: test</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>4aed5d81-569f-4b75-bd6b-05c35abe84d5</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:20</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>更新设备信息</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>c9a03a3f-cff5-446c-abc4-23cbfdaca867</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:20</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>转让保管人: lan -&gt; test</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>380c2355-80e7-4f21-91d9-3daabe12e407</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:20</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>更新设备信息</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>d0c1e371-e4e4-422b-bab9-6783f14e20f6</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:20</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>转给自己: test -&gt; lan</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>8efd156e-ec1c-4597-ae3d-6c920ea32d4b</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:27</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>更新设备信息</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>d65697fe-1375-434a-93b3-3bb1b445326a</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:27</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>转给自己: lan -&gt; test</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2fae26b5-f83c-4547-90fe-07808a7f915d</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:27</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>更新设备信息</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>69829ba4-9aa1-4291-b10e-abf332ca95d9</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:27</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>未找到退回: test -&gt; lan</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>a1b07932-f397-46bb-9a67-e297e41620a1</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:37</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>更新设备信息</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>3f4e7be2-522b-4d19-8b35-3ef5bc842502</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:37</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>借出设备: lan</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>cb2b28ff-59f3-4acb-9904-71c4169d5607</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:38</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>更新设备信息</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>50e2d0e4-504a-4920-ac7b-20043b3ad156</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:38</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>保管人代还: lan</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
